--- a/模拟持仓.xlsx
+++ b/模拟持仓.xlsx
@@ -76,19 +76,19 @@
     <t>+0.00%</t>
   </si>
   <si>
-    <t>+0.14%</t>
-  </si>
-  <si>
-    <t>+0.23%</t>
-  </si>
-  <si>
-    <t>+0.44%</t>
-  </si>
-  <si>
-    <t>+0.16%</t>
-  </si>
-  <si>
-    <t>+0.19%</t>
+    <t>-2.52%</t>
+  </si>
+  <si>
+    <t>-1.83%</t>
+  </si>
+  <si>
+    <t>-3.54%</t>
+  </si>
+  <si>
+    <t>-3.17%</t>
+  </si>
+  <si>
+    <t>-2.20%</t>
   </si>
   <si>
     <t>N</t>
@@ -522,13 +522,13 @@
         <v>18</v>
       </c>
       <c r="F3">
-        <v>534.2</v>
+        <v>520.01</v>
       </c>
       <c r="G3">
-        <v>961560</v>
+        <v>936018</v>
       </c>
       <c r="H3">
-        <v>1350</v>
+        <v>-24192</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
@@ -560,13 +560,13 @@
         <v>18</v>
       </c>
       <c r="F4">
-        <v>279.8</v>
+        <v>274.06</v>
       </c>
       <c r="G4">
-        <v>979300</v>
+        <v>959210</v>
       </c>
       <c r="H4">
-        <v>2240</v>
+        <v>-17850</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -598,13 +598,13 @@
         <v>18</v>
       </c>
       <c r="F5">
-        <v>249.25</v>
+        <v>239.39</v>
       </c>
       <c r="G5">
-        <v>997000</v>
+        <v>957560</v>
       </c>
       <c r="H5">
-        <v>4320</v>
+        <v>-35120</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -636,13 +636,13 @@
         <v>18</v>
       </c>
       <c r="F6">
-        <v>1343.87</v>
+        <v>1299.2</v>
       </c>
       <c r="G6">
-        <v>940709</v>
+        <v>909440</v>
       </c>
       <c r="H6">
-        <v>1512</v>
+        <v>-29757</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
@@ -665,10 +665,10 @@
         <v>4861237</v>
       </c>
       <c r="G8">
-        <v>4870659</v>
+        <v>4754318</v>
       </c>
       <c r="H8">
-        <v>9422</v>
+        <v>-106919</v>
       </c>
       <c r="I8" t="s">
         <v>24</v>

--- a/模拟持仓.xlsx
+++ b/模拟持仓.xlsx
@@ -1,118 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
-  <si>
-    <t>标的</t>
-  </si>
-  <si>
-    <t>代码</t>
-  </si>
-  <si>
-    <t>成本</t>
-  </si>
-  <si>
-    <t>股数</t>
-  </si>
-  <si>
-    <t>持有人</t>
-  </si>
-  <si>
-    <t>现价</t>
-  </si>
-  <si>
-    <t>市值</t>
-  </si>
-  <si>
-    <t>盈亏</t>
-  </si>
-  <si>
-    <t>盈亏比</t>
-  </si>
-  <si>
-    <t>卖出？(Y/N)</t>
-  </si>
-  <si>
-    <t>建仓日期</t>
-  </si>
-  <si>
-    <t>持仓时间(天)</t>
-  </si>
-  <si>
-    <t>利通电子</t>
-  </si>
-  <si>
-    <t>江波龙</t>
-  </si>
-  <si>
-    <t>海光信息</t>
-  </si>
-  <si>
-    <t>澜起科技</t>
-  </si>
-  <si>
-    <t>寒武纪</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>模拟</t>
-  </si>
-  <si>
-    <t>+0.00%</t>
-  </si>
-  <si>
-    <t>-2.52%</t>
-  </si>
-  <si>
-    <t>-1.83%</t>
-  </si>
-  <si>
-    <t>-3.54%</t>
-  </si>
-  <si>
-    <t>-3.17%</t>
-  </si>
-  <si>
-    <t>-2.20%</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -130,14 +45,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -425,253 +409,336 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>股数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>持有人</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>现价</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>市值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>盈亏</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>卖出？(Y/N)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>建仓日期</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>持仓时间(天)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>利通电子</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>603629</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>180.38</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>模拟</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>180.38</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>992090</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>603629</v>
-      </c>
-      <c r="C2">
-        <v>180.38</v>
-      </c>
-      <c r="D2">
-        <v>5500</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>180.38</v>
-      </c>
-      <c r="G2">
-        <v>992090</v>
-      </c>
-      <c r="H2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>江波龙</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>301308</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>533.45</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>模拟</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>520.01</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>936018</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>-24192</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.52%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>688041</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>模拟</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>274.06</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>959210</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>-17850</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.83%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>301308</v>
-      </c>
-      <c r="C3">
-        <v>533.45</v>
-      </c>
-      <c r="D3">
-        <v>1800</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>520.01</v>
-      </c>
-      <c r="G3">
-        <v>936018</v>
-      </c>
-      <c r="H3">
-        <v>-24192</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>688008</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>248.17</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>模拟</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>239.39</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>957560</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>-35120</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-3.54%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>688041</v>
-      </c>
-      <c r="C4">
-        <v>279.16</v>
-      </c>
-      <c r="D4">
-        <v>3500</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>274.06</v>
-      </c>
-      <c r="G4">
-        <v>959210</v>
-      </c>
-      <c r="H4">
-        <v>-17850</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>寒武纪</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>688256</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>1341.71</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>模拟</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1299.2</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>909440</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>-29757</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-3.17%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>688008</v>
-      </c>
-      <c r="C5">
-        <v>248.17</v>
-      </c>
-      <c r="D5">
-        <v>4000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>239.39</v>
-      </c>
-      <c r="G5">
-        <v>957560</v>
-      </c>
-      <c r="H5">
-        <v>-35120</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>688256</v>
-      </c>
-      <c r="C6">
-        <v>1341.71</v>
-      </c>
-      <c r="D6">
-        <v>700</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>1299.2</v>
-      </c>
-      <c r="G6">
-        <v>909440</v>
-      </c>
-      <c r="H6">
-        <v>-29757</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>4861237</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1" t="n">
         <v>4754318</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1" t="n">
         <v>-106919</v>
       </c>
-      <c r="I8" t="s">
-        <v>24</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.20%</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/模拟持仓.xlsx
+++ b/模拟持仓.xlsx
@@ -45,10 +45,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,268 +474,6 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>持仓时间(天)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>利通电子</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>603629</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>180.38</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>模拟</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>180.38</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>992090</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>江波龙</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>301308</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>533.45</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>模拟</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>520.01</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>936018</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>-24192</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.52%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>海光信息</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>688041</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>279.16</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>模拟</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>274.06</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>959210</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>-17850</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.83%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>澜起科技</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>688008</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>248.17</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>模拟</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>239.39</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>957560</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>-35120</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-3.54%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>寒武纪</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>688256</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>1341.71</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>700</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>模拟</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>1299.2</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>909440</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>-29757</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-3.17%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>4861237</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>4754318</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>-106919</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.20%</t>
         </is>
       </c>
     </row>
